--- a/astro-site/public/dl/pizza-shop-checklist-templates/03-pizzeria-manager-checklist.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/03-pizzeria-manager-checklist.xlsx
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>Weekly flour order (00, semolina)</t>
+          <t>Weekly flour order (00 or high-gluten, semolina)</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
@@ -2392,9 +2392,9 @@
       <c r="A14" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>Dish machine: filters, rinse aid, softener salt</t>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Dish machine: filters, rinse aid and chemical levels (water softener salt only if you have a softener)</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
